--- a/TextFiles/Database missioni.xlsx
+++ b/TextFiles/Database missioni.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefy\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefy\Desktop\Progetto Serious Game\ProgettoSeriousGame\TextFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F2543C-B257-4C32-BC0D-5743612BCA79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AD5427-0814-41E8-8334-E668D6EF6828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="-20850" windowWidth="20090" windowHeight="14460" xr2:uid="{A01D3E12-92BC-4039-ADA7-2749234A279B}"/>
+    <workbookView xWindow="17850" yWindow="-19280" windowWidth="17410" windowHeight="12940" xr2:uid="{A01D3E12-92BC-4039-ADA7-2749234A279B}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>Missioni</t>
   </si>
@@ -129,6 +129,21 @@
   </si>
   <si>
     <t>Recupero Dati di bordo</t>
+  </si>
+  <si>
+    <t>Potenziamenti</t>
+  </si>
+  <si>
+    <t>Radiation Shield</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>Speed1</t>
+  </si>
+  <si>
+    <t>Armor</t>
   </si>
 </sst>
 </file>
@@ -500,20 +515,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E66CEEBA-BBC5-4F9B-9447-3E2AB89B1B48}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="18.73046875" customWidth="1"/>
+    <col min="3" max="3" width="15.6640625" customWidth="1"/>
     <col min="8" max="8" width="17.86328125" customWidth="1"/>
+    <col min="9" max="9" width="14.6640625" customWidth="1"/>
     <col min="14" max="14" width="20.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>25</v>
       </c>
@@ -524,59 +541,83 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
       <c r="G5" t="s">
         <v>1</v>
       </c>
       <c r="H5" t="s">
         <v>27</v>
       </c>
+      <c r="I5" t="s">
+        <v>31</v>
+      </c>
       <c r="M5" t="s">
         <v>1</v>
       </c>
       <c r="N5" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>2</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
       </c>
+      <c r="C7" t="s">
+        <v>32</v>
+      </c>
       <c r="G7" t="s">
         <v>10</v>
       </c>
       <c r="H7" t="s">
         <v>20</v>
       </c>
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
       <c r="M7" t="s">
         <v>21</v>
       </c>
       <c r="N7" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
         <v>13</v>
       </c>
+      <c r="C8" t="s">
+        <v>32</v>
+      </c>
       <c r="G8" t="s">
         <v>23</v>
       </c>
       <c r="H8" t="s">
         <v>24</v>
       </c>
+      <c r="I8" t="s">
+        <v>33</v>
+      </c>
       <c r="M8" t="s">
         <v>29</v>
       </c>
@@ -584,23 +625,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>4</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>5</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>6</v>
       </c>
@@ -608,7 +655,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -616,7 +663,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>8</v>
       </c>
@@ -624,7 +671,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>9</v>
       </c>

--- a/TextFiles/Database missioni.xlsx
+++ b/TextFiles/Database missioni.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefy\Desktop\Progetto Serious Game\ProgettoSeriousGame\TextFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AD5427-0814-41E8-8334-E668D6EF6828}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354BFF0B-1B92-4B0B-99EC-7A3BFAB5034D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17850" yWindow="-19280" windowWidth="17410" windowHeight="12940" xr2:uid="{A01D3E12-92BC-4039-ADA7-2749234A279B}"/>
+    <workbookView xWindow="14317" yWindow="2925" windowWidth="14565" windowHeight="14438" xr2:uid="{A01D3E12-92BC-4039-ADA7-2749234A279B}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
   <si>
     <t>Missioni</t>
   </si>
@@ -144,6 +144,18 @@
   </si>
   <si>
     <t>Armor</t>
+  </si>
+  <si>
+    <t>M_R002</t>
+  </si>
+  <si>
+    <t>M_R003</t>
+  </si>
+  <si>
+    <t>M_C002</t>
+  </si>
+  <si>
+    <t>M_C003</t>
   </si>
 </sst>
 </file>
@@ -635,6 +647,18 @@
       <c r="C9" t="s">
         <v>32</v>
       </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -645,6 +669,18 @@
       </c>
       <c r="C10" t="s">
         <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M10" t="s">
+        <v>37</v>
+      </c>
+      <c r="N10" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.45">

--- a/TextFiles/Database missioni.xlsx
+++ b/TextFiles/Database missioni.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefy\Desktop\Progetto Serious Game\ProgettoSeriousGame\TextFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354BFF0B-1B92-4B0B-99EC-7A3BFAB5034D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81AFFC5-BAA3-4C1D-A470-8C8913C6400F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14317" yWindow="2925" windowWidth="14565" windowHeight="14438" xr2:uid="{A01D3E12-92BC-4039-ADA7-2749234A279B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="43">
   <si>
     <t>Missioni</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>M_C003</t>
+  </si>
+  <si>
+    <t>Speed2</t>
+  </si>
+  <si>
+    <t>Magnetic Shield</t>
+  </si>
+  <si>
+    <t>Fine Gioco</t>
   </si>
 </sst>
 </file>
@@ -659,6 +668,9 @@
       <c r="N9" t="s">
         <v>22</v>
       </c>
+      <c r="O9" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -676,6 +688,9 @@
       <c r="H10" t="s">
         <v>24</v>
       </c>
+      <c r="I10" t="s">
+        <v>40</v>
+      </c>
       <c r="M10" t="s">
         <v>37</v>
       </c>
@@ -690,6 +705,9 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
+      <c r="C11" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -698,6 +716,9 @@
       <c r="B12" t="s">
         <v>17</v>
       </c>
+      <c r="C12" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -706,6 +727,9 @@
       <c r="B13" t="s">
         <v>18</v>
       </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -713,6 +737,9 @@
       </c>
       <c r="B14" t="s">
         <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
